--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/115.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/115.xlsx
@@ -426,13 +426,13 @@
         <v>-21.81312935771117</v>
       </c>
       <c r="E2">
-        <v>-11.30089500385512</v>
+        <v>-14.39913200873494</v>
       </c>
       <c r="F2">
-        <v>-3.442621348583404</v>
+        <v>-4.585792387101403</v>
       </c>
       <c r="G2">
-        <v>-9.084270532250041</v>
+        <v>-10.07210090516763</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.97943629797491</v>
       </c>
       <c r="E3">
-        <v>-12.4991292262847</v>
+        <v>-14.609937002266</v>
       </c>
       <c r="F3">
-        <v>-3.406919541890148</v>
+        <v>-4.540761506717819</v>
       </c>
       <c r="G3">
-        <v>-7.466605559940569</v>
+        <v>-10.61415638958574</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.05222041351511</v>
       </c>
       <c r="E4">
-        <v>-11.00708761023747</v>
+        <v>-14.98278890968754</v>
       </c>
       <c r="F4">
-        <v>-3.528687064999467</v>
+        <v>-4.331665006903168</v>
       </c>
       <c r="G4">
-        <v>-8.72665878200689</v>
+        <v>-9.947164227061077</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.98555898732311</v>
       </c>
       <c r="E5">
-        <v>-13.23213067153626</v>
+        <v>-15.40456192181394</v>
       </c>
       <c r="F5">
-        <v>-3.742289883485348</v>
+        <v>-4.488641458101077</v>
       </c>
       <c r="G5">
-        <v>-7.435754586060101</v>
+        <v>-10.2740044565167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.75927245869173</v>
       </c>
       <c r="E6">
-        <v>-14.38887954358157</v>
+        <v>-17.005726176024</v>
       </c>
       <c r="F6">
-        <v>-3.754970531687402</v>
+        <v>-4.146270583584819</v>
       </c>
       <c r="G6">
-        <v>-8.499840064929264</v>
+        <v>-10.33990748656698</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.36859259998052</v>
       </c>
       <c r="E7">
-        <v>-13.58515239127821</v>
+        <v>-16.93977348057629</v>
       </c>
       <c r="F7">
-        <v>-3.666013813035569</v>
+        <v>-4.595571264291451</v>
       </c>
       <c r="G7">
-        <v>-7.570927470974083</v>
+        <v>-10.63994553933666</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.8168270558817</v>
       </c>
       <c r="E8">
-        <v>-14.20326192248117</v>
+        <v>-17.49272732775689</v>
       </c>
       <c r="F8">
-        <v>-3.697675671905372</v>
+        <v>-4.034686180958114</v>
       </c>
       <c r="G8">
-        <v>-8.690401687260792</v>
+        <v>-10.37310232668925</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.09776136914685</v>
       </c>
       <c r="E9">
-        <v>-16.57755443012476</v>
+        <v>-17.66709621942224</v>
       </c>
       <c r="F9">
-        <v>-3.240109541253606</v>
+        <v>-3.869559422884061</v>
       </c>
       <c r="G9">
-        <v>-6.458700038872839</v>
+        <v>-8.728532550782118</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.22360126550344</v>
       </c>
       <c r="E10">
-        <v>-16.5628776458659</v>
+        <v>-18.28516046588512</v>
       </c>
       <c r="F10">
-        <v>-3.163438339552692</v>
+        <v>-4.156687303675023</v>
       </c>
       <c r="G10">
-        <v>-6.710414058405784</v>
+        <v>-9.889908341959382</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.21774571797397</v>
       </c>
       <c r="E11">
-        <v>-16.91450006713949</v>
+        <v>-19.5453306273176</v>
       </c>
       <c r="F11">
-        <v>-3.054572638741976</v>
+        <v>-3.906367928427457</v>
       </c>
       <c r="G11">
-        <v>-6.522202923407138</v>
+        <v>-9.913234445829087</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.10749324116593</v>
       </c>
       <c r="E12">
-        <v>-17.1750458191708</v>
+        <v>-18.84492060949924</v>
       </c>
       <c r="F12">
-        <v>-3.705656163463942</v>
+        <v>-4.386483048150827</v>
       </c>
       <c r="G12">
-        <v>-6.714174838138396</v>
+        <v>-9.251575572168189</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.91652484233422</v>
       </c>
       <c r="E13">
-        <v>-17.5240236116239</v>
+        <v>-19.47192406365327</v>
       </c>
       <c r="F13">
-        <v>-3.534859230517726</v>
+        <v>-4.062217799957558</v>
       </c>
       <c r="G13">
-        <v>-6.348356245503391</v>
+        <v>-8.598901519100876</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.70034023838234</v>
       </c>
       <c r="E14">
-        <v>-19.13420405758323</v>
+        <v>-20.05286840867527</v>
       </c>
       <c r="F14">
-        <v>-3.529918018960027</v>
+        <v>-3.742544192278007</v>
       </c>
       <c r="G14">
-        <v>-5.770149603796442</v>
+        <v>-8.194584592389685</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.50975979655814</v>
       </c>
       <c r="E15">
-        <v>-18.78316580945664</v>
+        <v>-21.59903434606218</v>
       </c>
       <c r="F15">
-        <v>-2.899708524421205</v>
+        <v>-3.846997179934011</v>
       </c>
       <c r="G15">
-        <v>-6.714750873062229</v>
+        <v>-6.815090197811999</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.38561999296156</v>
       </c>
       <c r="E16">
-        <v>-19.80482124490513</v>
+        <v>-21.90275004080861</v>
       </c>
       <c r="F16">
-        <v>-2.744436853338257</v>
+        <v>-3.766371352252132</v>
       </c>
       <c r="G16">
-        <v>-5.869161399784964</v>
+        <v>-6.980322836222564</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.37299894308976</v>
       </c>
       <c r="E17">
-        <v>-20.50609620125895</v>
+        <v>-23.6303311754168</v>
       </c>
       <c r="F17">
-        <v>-2.359905391489116</v>
+        <v>-3.462623107891401</v>
       </c>
       <c r="G17">
-        <v>-3.83142461454291</v>
+        <v>-6.922428015831789</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.5090274944327</v>
       </c>
       <c r="E18">
-        <v>-22.67069771997737</v>
+        <v>-23.99683869075359</v>
       </c>
       <c r="F18">
-        <v>-2.623245873941287</v>
+        <v>-3.316065033518501</v>
       </c>
       <c r="G18">
-        <v>-4.06222260735874</v>
+        <v>-7.33832854138489</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.811686118408385</v>
       </c>
       <c r="E19">
-        <v>-23.30991899700408</v>
+        <v>-24.1114951241538</v>
       </c>
       <c r="F19">
-        <v>-2.477846685564904</v>
+        <v>-3.549288562307091</v>
       </c>
       <c r="G19">
-        <v>-4.222684749647215</v>
+        <v>-7.446825050343424</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.277304338104623</v>
       </c>
       <c r="E20">
-        <v>-22.54667187385529</v>
+        <v>-24.21425525633585</v>
       </c>
       <c r="F20">
-        <v>-2.654819925866393</v>
+        <v>-2.727216751768861</v>
       </c>
       <c r="G20">
-        <v>-4.868684742907359</v>
+        <v>-7.49390100791186</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.910325396841415</v>
       </c>
       <c r="E21">
-        <v>-25.50311330060693</v>
+        <v>-26.06812647406995</v>
       </c>
       <c r="F21">
-        <v>-1.972139983299445</v>
+        <v>-2.876464535098651</v>
       </c>
       <c r="G21">
-        <v>-4.911817840738522</v>
+        <v>-6.532502030579811</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.701245296654088</v>
       </c>
       <c r="E22">
-        <v>-22.98254202556757</v>
+        <v>-26.54948514718928</v>
       </c>
       <c r="F22">
-        <v>-2.064966006089755</v>
+        <v>-2.449706216524402</v>
       </c>
       <c r="G22">
-        <v>-3.847811814962303</v>
+        <v>-6.798067372649067</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.62607168147176</v>
       </c>
       <c r="E23">
-        <v>-24.60207829882675</v>
+        <v>-27.24682033115643</v>
       </c>
       <c r="F23">
-        <v>-2.216178676898985</v>
+        <v>-2.442777751567387</v>
       </c>
       <c r="G23">
-        <v>-3.477914630222915</v>
+        <v>-6.743714835985313</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.661228278528833</v>
       </c>
       <c r="E24">
-        <v>-25.76035779508665</v>
+        <v>-27.40902574163718</v>
       </c>
       <c r="F24">
-        <v>-1.768009546064577</v>
+        <v>-2.517239697405034</v>
       </c>
       <c r="G24">
-        <v>-4.221098998333904</v>
+        <v>-6.307421349910302</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.779494627241185</v>
       </c>
       <c r="E25">
-        <v>-25.44985844627673</v>
+        <v>-27.48947408238344</v>
       </c>
       <c r="F25">
-        <v>-1.807429065661597</v>
+        <v>-1.992168250364331</v>
       </c>
       <c r="G25">
-        <v>-3.778568444462906</v>
+        <v>-7.275424865593197</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.948526058700324</v>
       </c>
       <c r="E26">
-        <v>-25.80382208861227</v>
+        <v>-28.28550282887376</v>
       </c>
       <c r="F26">
-        <v>-1.710550669536792</v>
+        <v>-2.085299112358871</v>
       </c>
       <c r="G26">
-        <v>-4.135034745949471</v>
+        <v>-6.461858299317303</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.132552164423297</v>
       </c>
       <c r="E27">
-        <v>-26.74332647708761</v>
+        <v>-28.3907898495521</v>
       </c>
       <c r="F27">
-        <v>-1.320100522594647</v>
+        <v>-2.10967796502326</v>
       </c>
       <c r="G27">
-        <v>-4.998848772420423</v>
+        <v>-5.996388975404696</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.308280326636751</v>
       </c>
       <c r="E28">
-        <v>-25.16694656112153</v>
+        <v>-28.65647089110811</v>
       </c>
       <c r="F28">
-        <v>-0.8020403772512394</v>
+        <v>-2.502580079477692</v>
       </c>
       <c r="G28">
-        <v>-3.422055795338792</v>
+        <v>-7.061391475388237</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.458521586226301</v>
       </c>
       <c r="E29">
-        <v>-26.19967864399278</v>
+        <v>-27.2791536355712</v>
       </c>
       <c r="F29">
-        <v>-1.267650783751591</v>
+        <v>-2.2689713598468</v>
       </c>
       <c r="G29">
-        <v>-4.952600451236805</v>
+        <v>-6.196849128898645</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.567110444246449</v>
       </c>
       <c r="E30">
-        <v>-25.38604319056063</v>
+        <v>-28.54378887237525</v>
       </c>
       <c r="F30">
-        <v>-0.8667458118187145</v>
+        <v>-2.078962930094858</v>
       </c>
       <c r="G30">
-        <v>-4.105653654288439</v>
+        <v>-6.8565150541449</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.627178204530566</v>
       </c>
       <c r="E31">
-        <v>-26.87885917566318</v>
+        <v>-29.49861308841853</v>
       </c>
       <c r="F31">
-        <v>-1.857812027834668</v>
+        <v>-2.05308141896179</v>
       </c>
       <c r="G31">
-        <v>-4.481324430448316</v>
+        <v>-7.299515705482474</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.641375851494951</v>
       </c>
       <c r="E32">
-        <v>-26.57350870179997</v>
+        <v>-28.57607689204994</v>
       </c>
       <c r="F32">
-        <v>-1.010003670458861</v>
+        <v>-2.130371411112595</v>
       </c>
       <c r="G32">
-        <v>-3.255396311800802</v>
+        <v>-6.574542648383016</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.616560994940901</v>
       </c>
       <c r="E33">
-        <v>-27.21286583304692</v>
+        <v>-28.10993842007039</v>
       </c>
       <c r="F33">
-        <v>-1.599430152655655</v>
+        <v>-1.955749905867654</v>
       </c>
       <c r="G33">
-        <v>-4.244090737104142</v>
+        <v>-6.586165973771397</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.558786381051192</v>
       </c>
       <c r="E34">
-        <v>-26.17419239227761</v>
+        <v>-27.6776050065581</v>
       </c>
       <c r="F34">
-        <v>-1.160049999964949</v>
+        <v>-1.709013219637196</v>
       </c>
       <c r="G34">
-        <v>-5.022171565744588</v>
+        <v>-5.765379107674352</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.479708668103498</v>
       </c>
       <c r="E35">
-        <v>-26.78876518528057</v>
+        <v>-27.81135348637464</v>
       </c>
       <c r="F35">
-        <v>-0.8681465810968484</v>
+        <v>-1.799454372674846</v>
       </c>
       <c r="G35">
-        <v>-5.016642954694006</v>
+        <v>-6.844332246560382</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.393494819689792</v>
       </c>
       <c r="E36">
-        <v>-23.90462084606139</v>
+        <v>-27.90083613276621</v>
       </c>
       <c r="F36">
-        <v>-1.797559896424643</v>
+        <v>-1.962553287346846</v>
       </c>
       <c r="G36">
-        <v>-4.991439771503535</v>
+        <v>-6.482876952946136</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.306426509254097</v>
       </c>
       <c r="E37">
-        <v>-26.25279311562874</v>
+        <v>-27.39179489803799</v>
       </c>
       <c r="F37">
-        <v>-1.498959955472311</v>
+        <v>-2.167388665241496</v>
       </c>
       <c r="G37">
-        <v>-6.19818658929651</v>
+        <v>-7.498330517843405</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.224432749908328</v>
       </c>
       <c r="E38">
-        <v>-24.06496958219899</v>
+        <v>-27.23647729652291</v>
       </c>
       <c r="F38">
-        <v>-0.9215936742928753</v>
+        <v>-2.353849197407249</v>
       </c>
       <c r="G38">
-        <v>-5.818705375220933</v>
+        <v>-7.08640264693743</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.154659701574481</v>
       </c>
       <c r="E39">
-        <v>-23.98459369703685</v>
+        <v>-25.87342020563616</v>
       </c>
       <c r="F39">
-        <v>-1.004823889089156</v>
+        <v>-2.101574046721673</v>
       </c>
       <c r="G39">
-        <v>-4.938782234155886</v>
+        <v>-6.616695824734556</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.100130844083848</v>
       </c>
       <c r="E40">
-        <v>-25.48401219724258</v>
+        <v>-25.72250880933055</v>
       </c>
       <c r="F40">
-        <v>-1.667255218862073</v>
+        <v>-1.648516719843345</v>
       </c>
       <c r="G40">
-        <v>-5.097075969116139</v>
+        <v>-6.960995871364299</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.057544301817121</v>
       </c>
       <c r="E41">
-        <v>-23.94030974971584</v>
+        <v>-25.1708863335082</v>
       </c>
       <c r="F41">
-        <v>-1.535285522819875</v>
+        <v>-1.719951811191163</v>
       </c>
       <c r="G41">
-        <v>-3.68793232868874</v>
+        <v>-7.11256919887983</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.026741505371586</v>
       </c>
       <c r="E42">
-        <v>-23.90534540190262</v>
+        <v>-25.24317436409265</v>
       </c>
       <c r="F42">
-        <v>-1.137913537859938</v>
+        <v>-2.038545227777464</v>
       </c>
       <c r="G42">
-        <v>-5.866122318979913</v>
+        <v>-7.830424583069854</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.008657167748323</v>
       </c>
       <c r="E43">
-        <v>-21.14642242594354</v>
+        <v>-25.67546702133886</v>
       </c>
       <c r="F43">
-        <v>-0.7332063595482118</v>
+        <v>-1.41689525361177</v>
       </c>
       <c r="G43">
-        <v>-4.546747431395393</v>
+        <v>-6.807174683427602</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.997424202480735</v>
       </c>
       <c r="E44">
-        <v>-22.06652230329601</v>
+        <v>-23.43621813707801</v>
       </c>
       <c r="F44">
-        <v>-1.490353218157224</v>
+        <v>-1.911768566983417</v>
       </c>
       <c r="G44">
-        <v>-4.473144072420776</v>
+        <v>-7.181322608639414</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.990013927495095</v>
       </c>
       <c r="E45">
-        <v>-22.16836315525451</v>
+        <v>-24.19856409389928</v>
       </c>
       <c r="F45">
-        <v>-1.349421415184139</v>
+        <v>-1.687609862683662</v>
       </c>
       <c r="G45">
-        <v>-4.488120980440439</v>
+        <v>-6.169312011102987</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.987191904503893</v>
       </c>
       <c r="E46">
-        <v>-21.73719355956219</v>
+        <v>-21.7642964764981</v>
       </c>
       <c r="F46">
-        <v>-0.3527827716495528</v>
+        <v>-1.863287536367173</v>
       </c>
       <c r="G46">
-        <v>-5.255819938269731</v>
+        <v>-6.498969514812533</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.987850723039875</v>
       </c>
       <c r="E47">
-        <v>-19.69943006932462</v>
+        <v>-21.878183069317</v>
       </c>
       <c r="F47">
-        <v>-1.105030665438409</v>
+        <v>-1.562890038150766</v>
       </c>
       <c r="G47">
-        <v>-4.50751084566395</v>
+        <v>-7.130111779692428</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.98803152016257</v>
       </c>
       <c r="E48">
-        <v>-19.63397550601775</v>
+        <v>-21.80797813677609</v>
       </c>
       <c r="F48">
-        <v>-1.272064325273707</v>
+        <v>-1.886613534062604</v>
       </c>
       <c r="G48">
-        <v>-4.784567091300017</v>
+        <v>-7.542304494241544</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.988482992853653</v>
       </c>
       <c r="E49">
-        <v>-18.60508809757901</v>
+        <v>-22.43851380065609</v>
       </c>
       <c r="F49">
-        <v>-1.014493421782034</v>
+        <v>-1.717501500413682</v>
       </c>
       <c r="G49">
-        <v>-6.179210542265408</v>
+        <v>-7.20863791988394</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.991753643941284</v>
       </c>
       <c r="E50">
-        <v>-18.08987908125235</v>
+        <v>-20.73882806593516</v>
       </c>
       <c r="F50">
-        <v>-1.004317756606045</v>
+        <v>-1.714304002238876</v>
       </c>
       <c r="G50">
-        <v>-5.7699774554284</v>
+        <v>-7.598143465852432</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.993794323975802</v>
       </c>
       <c r="E51">
-        <v>-18.8461387690073</v>
+        <v>-20.98065310641876</v>
       </c>
       <c r="F51">
-        <v>-1.000255442862716</v>
+        <v>-1.937209386658195</v>
       </c>
       <c r="G51">
-        <v>-5.479715443636181</v>
+        <v>-6.181769593967265</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.992553607320691</v>
       </c>
       <c r="E52">
-        <v>-16.34926499845009</v>
+        <v>-18.83589536080196</v>
       </c>
       <c r="F52">
-        <v>-1.068237070508263</v>
+        <v>-1.937163826451041</v>
       </c>
       <c r="G52">
-        <v>-6.736699789987597</v>
+        <v>-7.584904594240886</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.988795931528493</v>
       </c>
       <c r="E53">
-        <v>-18.31096371078082</v>
+        <v>-18.65688025480474</v>
       </c>
       <c r="F53">
-        <v>-1.317911975916451</v>
+        <v>-1.753768253675647</v>
       </c>
       <c r="G53">
-        <v>-5.782024530645808</v>
+        <v>-8.035883660328103</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.980048570272713</v>
       </c>
       <c r="E54">
-        <v>-16.88101653032677</v>
+        <v>-19.69519594612744</v>
       </c>
       <c r="F54">
-        <v>-1.20603847306617</v>
+        <v>-1.892387254860117</v>
       </c>
       <c r="G54">
-        <v>-6.532968817500849</v>
+        <v>-8.727893615493038</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.961378399887767</v>
       </c>
       <c r="E55">
-        <v>-16.45003713054277</v>
+        <v>-18.10946473133552</v>
       </c>
       <c r="F55">
-        <v>-0.6189024267381164</v>
+        <v>-1.770579141748061</v>
       </c>
       <c r="G55">
-        <v>-7.785814981928175</v>
+        <v>-7.993303423601997</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.932618109525961</v>
       </c>
       <c r="E56">
-        <v>-14.7961433249874</v>
+        <v>-18.03130779843714</v>
       </c>
       <c r="F56">
-        <v>-1.476769649486118</v>
+        <v>-1.891037015993553</v>
       </c>
       <c r="G56">
-        <v>-4.923027347934495</v>
+        <v>-7.412766157835402</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.896162658325009</v>
       </c>
       <c r="E57">
-        <v>-13.88183536589074</v>
+        <v>-17.4640439733923</v>
       </c>
       <c r="F57">
-        <v>-0.6047928447662324</v>
+        <v>-1.660726026993207</v>
       </c>
       <c r="G57">
-        <v>-6.213885196243734</v>
+        <v>-8.492861434932481</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.849442383546901</v>
       </c>
       <c r="E58">
-        <v>-14.15163731879373</v>
+        <v>-16.21356474633624</v>
       </c>
       <c r="F58">
-        <v>-0.484481591551035</v>
+        <v>-1.820460113275036</v>
       </c>
       <c r="G58">
-        <v>-5.644636890766054</v>
+        <v>-8.753186183413069</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.793237477869713</v>
       </c>
       <c r="E59">
-        <v>-13.54650186562275</v>
+        <v>-16.6742826349286</v>
       </c>
       <c r="F59">
-        <v>-1.151973417787654</v>
+        <v>-1.59859432994623</v>
       </c>
       <c r="G59">
-        <v>-6.509222274347656</v>
+        <v>-8.186006968897434</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.731511549284583</v>
       </c>
       <c r="E60">
-        <v>-12.77693752123325</v>
+        <v>-16.32882799525347</v>
       </c>
       <c r="F60">
-        <v>-0.6602006836046858</v>
+        <v>-1.948801560092972</v>
       </c>
       <c r="G60">
-        <v>-6.794591299832832</v>
+        <v>-8.284876411427767</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.664537799148336</v>
       </c>
       <c r="E61">
-        <v>-14.11699902110906</v>
+        <v>-15.03320893928894</v>
       </c>
       <c r="F61">
-        <v>-0.969658036105511</v>
+        <v>-2.085710810958063</v>
       </c>
       <c r="G61">
-        <v>-6.470697455907157</v>
+        <v>-8.25247941278046</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.591023438461544</v>
       </c>
       <c r="E62">
-        <v>-11.71799463080561</v>
+        <v>-15.58025765636354</v>
       </c>
       <c r="F62">
-        <v>-0.7674121347120118</v>
+        <v>-1.876734424416817</v>
       </c>
       <c r="G62">
-        <v>-6.568179779856536</v>
+        <v>-7.889928328592715</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.513849616471884</v>
       </c>
       <c r="E63">
-        <v>-11.81879393374235</v>
+        <v>-15.30237237735685</v>
       </c>
       <c r="F63">
-        <v>-2.022979375911459</v>
+        <v>-2.024779418277742</v>
       </c>
       <c r="G63">
-        <v>-6.63898241730493</v>
+        <v>-8.989678314556446</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.437366912121936</v>
       </c>
       <c r="E64">
-        <v>-12.28135038278183</v>
+        <v>-15.12229307996783</v>
       </c>
       <c r="F64">
-        <v>-1.744293387322427</v>
+        <v>-1.735087740375116</v>
       </c>
       <c r="G64">
-        <v>-7.054479056302238</v>
+        <v>-7.970553354656126</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.360352991899745</v>
       </c>
       <c r="E65">
-        <v>-13.0008977317566</v>
+        <v>-15.1503198056013</v>
       </c>
       <c r="F65">
-        <v>-0.9045723809001511</v>
+        <v>-2.549156693434899</v>
       </c>
       <c r="G65">
-        <v>-6.119726660015783</v>
+        <v>-8.939122973626237</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.285013249816307</v>
       </c>
       <c r="E66">
-        <v>-12.368238213567</v>
+        <v>-14.60360166712927</v>
       </c>
       <c r="F66">
-        <v>-1.57832252286492</v>
+        <v>-1.899222114300615</v>
       </c>
       <c r="G66">
-        <v>-7.341000151635081</v>
+        <v>-7.941715192463534</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.217315978368575</v>
       </c>
       <c r="E67">
-        <v>-11.6566473934237</v>
+        <v>-13.71297309861872</v>
       </c>
       <c r="F67">
-        <v>-1.088401189827209</v>
+        <v>-2.150058390807528</v>
       </c>
       <c r="G67">
-        <v>-5.96402839275832</v>
+        <v>-9.085031957724075</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.159419995078931</v>
       </c>
       <c r="E68">
-        <v>-12.53542041698217</v>
+        <v>-13.48965140293045</v>
       </c>
       <c r="F68">
-        <v>-1.95081614961658</v>
+        <v>-2.101275834456665</v>
       </c>
       <c r="G68">
-        <v>-6.588096021820792</v>
+        <v>-8.436025989114272</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.111949903227696</v>
       </c>
       <c r="E69">
-        <v>-13.59137451456475</v>
+        <v>-13.66626641770361</v>
       </c>
       <c r="F69">
-        <v>-0.949008493488525</v>
+        <v>-2.078956303155636</v>
       </c>
       <c r="G69">
-        <v>-6.227127378400819</v>
+        <v>-9.066089016148364</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.078139887236221</v>
       </c>
       <c r="E70">
-        <v>-11.82551418916973</v>
+        <v>-13.6510915013039</v>
       </c>
       <c r="F70">
-        <v>-1.40969922598365</v>
+        <v>-2.428462734479608</v>
       </c>
       <c r="G70">
-        <v>-7.47150847788423</v>
+        <v>-8.721702895334602</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.061244012505592</v>
       </c>
       <c r="E71">
-        <v>-9.862959595251541</v>
+        <v>-14.10022555338465</v>
       </c>
       <c r="F71">
-        <v>-1.468572125668014</v>
+        <v>-2.335452814125877</v>
       </c>
       <c r="G71">
-        <v>-6.806452984500041</v>
+        <v>-8.507815169133368</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.05751916249322</v>
       </c>
       <c r="E72">
-        <v>-9.654572806840575</v>
+        <v>-13.32015967777137</v>
       </c>
       <c r="F72">
-        <v>-1.644925747152209</v>
+        <v>-2.021325954575471</v>
       </c>
       <c r="G72">
-        <v>-6.600437735591195</v>
+        <v>-8.930237469398833</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.064994787555568</v>
       </c>
       <c r="E73">
-        <v>-11.46566805909822</v>
+        <v>-14.31718021461813</v>
       </c>
       <c r="F73">
-        <v>-1.487453932247426</v>
+        <v>-2.56342200847851</v>
       </c>
       <c r="G73">
-        <v>-6.5014789083313</v>
+        <v>-8.277440926146564</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.084633763313073</v>
       </c>
       <c r="E74">
-        <v>-13.08202534360401</v>
+        <v>-13.20667159066514</v>
       </c>
       <c r="F74">
-        <v>-2.336975353412222</v>
+        <v>-3.072843110178122</v>
       </c>
       <c r="G74">
-        <v>-5.874650284289077</v>
+        <v>-7.541678801134622</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.112169998713844</v>
       </c>
       <c r="E75">
-        <v>-13.21527569127971</v>
+        <v>-13.16793955247754</v>
       </c>
       <c r="F75">
-        <v>-1.681320897361608</v>
+        <v>-2.61926971040785</v>
       </c>
       <c r="G75">
-        <v>-6.270508767147429</v>
+        <v>-8.027527843386983</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.142057817826633</v>
       </c>
       <c r="E76">
-        <v>-11.81139440721381</v>
+        <v>-15.13268139934143</v>
       </c>
       <c r="F76">
-        <v>-1.779876737477082</v>
+        <v>-2.80944629874256</v>
       </c>
       <c r="G76">
-        <v>-5.137845337432263</v>
+        <v>-7.876676214799012</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.172081566711068</v>
       </c>
       <c r="E77">
-        <v>-12.46204555263589</v>
+        <v>-14.84976951418623</v>
       </c>
       <c r="F77">
-        <v>-2.135033462855551</v>
+        <v>-3.217589545041099</v>
       </c>
       <c r="G77">
-        <v>-4.386725591663641</v>
+        <v>-7.579875875566733</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.201945762678935</v>
       </c>
       <c r="E78">
-        <v>-12.21610865775332</v>
+        <v>-14.84351569158164</v>
       </c>
       <c r="F78">
-        <v>-2.362310970426845</v>
+        <v>-3.215738143895842</v>
       </c>
       <c r="G78">
-        <v>-6.59464428089747</v>
+        <v>-7.807426223208538</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.226121535460688</v>
       </c>
       <c r="E79">
-        <v>-12.05645277813889</v>
+        <v>-15.20670383547081</v>
       </c>
       <c r="F79">
-        <v>-1.888612384605559</v>
+        <v>-3.443076950654944</v>
       </c>
       <c r="G79">
-        <v>-5.658011494744709</v>
+        <v>-7.808538566509733</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.242005192729829</v>
       </c>
       <c r="E80">
-        <v>-13.57823288299449</v>
+        <v>-15.43132520319927</v>
       </c>
       <c r="F80">
-        <v>-2.406578924432451</v>
+        <v>-3.178121151767313</v>
       </c>
       <c r="G80">
-        <v>-4.911228563632533</v>
+        <v>-7.551921629033127</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.252002181994946</v>
       </c>
       <c r="E81">
-        <v>-14.43576736345699</v>
+        <v>-16.18936005276524</v>
       </c>
       <c r="F81">
-        <v>-2.929971270747679</v>
+        <v>-3.287494641795946</v>
       </c>
       <c r="G81">
-        <v>-5.799610148550417</v>
+        <v>-7.021012751445746</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.254598449582623</v>
       </c>
       <c r="E82">
-        <v>-15.21172138467131</v>
+        <v>-16.99696810729317</v>
       </c>
       <c r="F82">
-        <v>-2.575874855644794</v>
+        <v>-3.464952477028073</v>
       </c>
       <c r="G82">
-        <v>-5.375231315871243</v>
+        <v>-8.117885873335851</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.248421505658872</v>
       </c>
       <c r="E83">
-        <v>-16.49835141973061</v>
+        <v>-18.62497262694669</v>
       </c>
       <c r="F83">
-        <v>-3.161992010067404</v>
+        <v>-3.574701217490174</v>
       </c>
       <c r="G83">
-        <v>-4.379263622018124</v>
+        <v>-7.326420509080131</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.235923090775396</v>
       </c>
       <c r="E84">
-        <v>-17.10147623044218</v>
+        <v>-19.53393245824029</v>
       </c>
       <c r="F84">
-        <v>-3.257832461836502</v>
+        <v>-3.634168884969748</v>
       </c>
       <c r="G84">
-        <v>-5.373629011830236</v>
+        <v>-6.891970996870494</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.222076651472696</v>
       </c>
       <c r="E85">
-        <v>-16.64284143989335</v>
+        <v>-19.48187312104812</v>
       </c>
       <c r="F85">
-        <v>-2.286926223302479</v>
+        <v>-3.764544802128959</v>
       </c>
       <c r="G85">
-        <v>-4.424869697367124</v>
+        <v>-7.732720452569344</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.20730502214624</v>
       </c>
       <c r="E86">
-        <v>-18.75406130700934</v>
+        <v>-20.77754651870073</v>
       </c>
       <c r="F86">
-        <v>-3.019740617821659</v>
+        <v>-3.855274227022783</v>
       </c>
       <c r="G86">
-        <v>-5.105299364235688</v>
+        <v>-7.110927168292352</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.194466135981882</v>
       </c>
       <c r="E87">
-        <v>-18.94080651813766</v>
+        <v>-21.61514212810746</v>
       </c>
       <c r="F87">
-        <v>-3.516845552976448</v>
+        <v>-3.860228692458927</v>
       </c>
       <c r="G87">
-        <v>-5.851049405139612</v>
+        <v>-6.737918070746049</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.192574114832178</v>
       </c>
       <c r="E88">
-        <v>-20.00557755461317</v>
+        <v>-21.83637166880418</v>
       </c>
       <c r="F88">
-        <v>-3.866013182032676</v>
+        <v>-4.458683550978833</v>
       </c>
       <c r="G88">
-        <v>-3.995124470368792</v>
+        <v>-7.745495847805392</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.205371098640526</v>
       </c>
       <c r="E89">
-        <v>-22.14103834309223</v>
+        <v>-24.37862980586627</v>
       </c>
       <c r="F89">
-        <v>-3.62720728531662</v>
+        <v>-4.289448918954297</v>
       </c>
       <c r="G89">
-        <v>-5.414073946683512</v>
+        <v>-7.129386770219328</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.235887784714148</v>
       </c>
       <c r="E90">
-        <v>-23.05727996059016</v>
+        <v>-24.69417387472074</v>
       </c>
       <c r="F90">
-        <v>-3.952382080918164</v>
+        <v>-4.433166521502997</v>
       </c>
       <c r="G90">
-        <v>-6.648553204458962</v>
+        <v>-8.115681050006696</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.289311798081568</v>
       </c>
       <c r="E91">
-        <v>-27.09537910339192</v>
+        <v>-26.16658002747072</v>
       </c>
       <c r="F91">
-        <v>-4.036094405542873</v>
+        <v>-4.383126503434684</v>
       </c>
       <c r="G91">
-        <v>-5.916035414075505</v>
+        <v>-8.444040819864847</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.372167928955289</v>
       </c>
       <c r="E92">
-        <v>-27.47346592676633</v>
+        <v>-28.61159371369209</v>
       </c>
       <c r="F92">
-        <v>-3.962498103641151</v>
+        <v>-4.650341260229749</v>
       </c>
       <c r="G92">
-        <v>-7.089435106651403</v>
+        <v>-8.849019855683892</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.483356696647364</v>
       </c>
       <c r="E93">
-        <v>-28.65076048538443</v>
+        <v>-30.03974988267611</v>
       </c>
       <c r="F93">
-        <v>-3.782397776394094</v>
+        <v>-4.721490564823601</v>
       </c>
       <c r="G93">
-        <v>-7.180912100992544</v>
+        <v>-8.745055483568621</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.620666863551753</v>
       </c>
       <c r="E94">
-        <v>-31.20898828603458</v>
+        <v>-31.73161720702281</v>
       </c>
       <c r="F94">
-        <v>-4.41353172895444</v>
+        <v>-5.000430862205293</v>
       </c>
       <c r="G94">
-        <v>-5.54417838637687</v>
+        <v>-8.968573586743593</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.785794314135217</v>
       </c>
       <c r="E95">
-        <v>-33.08395992840742</v>
+        <v>-32.75503421886028</v>
       </c>
       <c r="F95">
-        <v>-3.585137818398045</v>
+        <v>-4.996278256415058</v>
       </c>
       <c r="G95">
-        <v>-7.563766760972639</v>
+        <v>-8.342148849257159</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.971830115364849</v>
       </c>
       <c r="E96">
-        <v>-34.84503139253933</v>
+        <v>-35.04771003946363</v>
       </c>
       <c r="F96">
-        <v>-4.45259008036384</v>
+        <v>-4.832303757398299</v>
       </c>
       <c r="G96">
-        <v>-7.269760522175504</v>
+        <v>-10.52563240186563</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.166712729465553</v>
       </c>
       <c r="E97">
-        <v>-36.09718162650423</v>
+        <v>-36.12047383256268</v>
       </c>
       <c r="F97">
-        <v>-4.704235671823287</v>
+        <v>-5.077982618455382</v>
       </c>
       <c r="G97">
-        <v>-8.436423254578985</v>
+        <v>-10.23400313476569</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.362263193486372</v>
       </c>
       <c r="E98">
-        <v>-38.11098269653021</v>
+        <v>-39.75948082530545</v>
       </c>
       <c r="F98">
-        <v>-4.751354038061926</v>
+        <v>-5.164074842628334</v>
       </c>
       <c r="G98">
-        <v>-7.480986569763163</v>
+        <v>-10.31269149168863</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.544108240940323</v>
       </c>
       <c r="E99">
-        <v>-40.10987376588595</v>
+        <v>-41.63524042215563</v>
       </c>
       <c r="F99">
-        <v>-4.727948517095826</v>
+        <v>-5.31466458115066</v>
       </c>
       <c r="G99">
-        <v>-8.752570421942766</v>
+        <v>-11.32155376041721</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.70008545695015</v>
       </c>
       <c r="E100">
-        <v>-42.57708150321892</v>
+        <v>-43.98346703341107</v>
       </c>
       <c r="F100">
-        <v>-4.493269546780517</v>
+        <v>-5.206079696889493</v>
       </c>
       <c r="G100">
-        <v>-8.459229602799024</v>
+        <v>-10.78968813516898</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.806789767645634</v>
       </c>
       <c r="E101">
-        <v>-45.39035975269207</v>
+        <v>-45.03910413781311</v>
       </c>
       <c r="F101">
-        <v>-4.578553284368338</v>
+        <v>-5.410828096206849</v>
       </c>
       <c r="G101">
-        <v>-7.775078882744319</v>
+        <v>-11.89024920478983</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.871841938560342</v>
       </c>
       <c r="E102">
-        <v>-47.23874245992887</v>
+        <v>-47.39823531447902</v>
       </c>
       <c r="F102">
-        <v>-5.428101213290025</v>
+        <v>-5.110374269007051</v>
       </c>
       <c r="G102">
-        <v>-8.929529012653429</v>
+        <v>-11.10956628735551</v>
       </c>
     </row>
   </sheetData>
